--- a/Research Assets/Engagement Metrics/youtube video metrics.xlsx
+++ b/Research Assets/Engagement Metrics/youtube video metrics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>video_id</t>
   </si>
@@ -61,6 +61,15 @@
     <t>-YGXo00-fHw</t>
   </si>
   <si>
+    <t>9lkDNN9BQOU</t>
+  </si>
+  <si>
+    <t>BCDdf4fSpYg</t>
+  </si>
+  <si>
+    <t>qKTyoG1PXJc</t>
+  </si>
+  <si>
     <t>Masculinity + Money | MENtality with Ebuka: ft Banky W, Seun Kuti &amp; Noble Igwe</t>
   </si>
   <si>
@@ -79,15 +88,36 @@
     <t>Masculinity + Young Boys | MENtality with Ebuka: ft Banky W, IK Osakioduwa, Murewa &amp; Sonariwo OnDeck</t>
   </si>
   <si>
+    <t>Episode 1: A Girl Dad on a Mission|Is my daughter really safe in this world?</t>
+  </si>
+  <si>
+    <t>Undoing My Father’s Damage - Onyango Otieno (Rix poet)</t>
+  </si>
+  <si>
+    <t>My voice was beaten out of me by my father  - Toxic masculinity</t>
+  </si>
+  <si>
     <t>Nigeria</t>
   </si>
   <si>
+    <t>Kenya</t>
+  </si>
+  <si>
     <t>Banky Wellington &amp; Ebuka (MENtality)</t>
   </si>
   <si>
     <t>Banky Wellington</t>
   </si>
   <si>
+    <t>Episode 1 A Girl Dad On A Mission</t>
+  </si>
+  <si>
+    <t>Undoing My Father S Damage</t>
+  </si>
+  <si>
+    <t>My Voice Was Beaten Out Of Me By My Father Toxic Masculinity</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=f6WW9g5hqLI</t>
   </si>
   <si>
@@ -104,6 +134,15 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=-YGXo00-fHw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=9lkDNN9BQOU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BCDdf4fSpYg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=qKTyoG1PXJc</t>
   </si>
 </sst>
 </file>
@@ -474,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -511,13 +550,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>252060</v>
@@ -532,7 +571,7 @@
         <v>6609</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -540,13 +579,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>134233</v>
@@ -561,7 +600,7 @@
         <v>4313</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -569,13 +608,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>86093</v>
@@ -590,7 +629,7 @@
         <v>4784</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -598,13 +637,13 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>48687</v>
@@ -619,7 +658,7 @@
         <v>3168</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -627,13 +666,13 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>63529</v>
@@ -648,7 +687,7 @@
         <v>6662</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -656,13 +695,13 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>65152</v>
@@ -677,7 +716,94 @@
         <v>6160</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>109792</v>
+      </c>
+      <c r="F8">
+        <v>2883</v>
+      </c>
+      <c r="G8">
+        <v>185</v>
+      </c>
+      <c r="H8">
+        <v>2776</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>52299</v>
+      </c>
+      <c r="F9">
+        <v>939</v>
+      </c>
+      <c r="G9">
+        <v>176</v>
+      </c>
+      <c r="H9">
+        <v>1541</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>36495</v>
+      </c>
+      <c r="F10">
+        <v>676</v>
+      </c>
+      <c r="G10">
+        <v>251</v>
+      </c>
+      <c r="H10">
+        <v>4283</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -688,6 +814,9 @@
     <hyperlink ref="I5" r:id="rId4"/>
     <hyperlink ref="I6" r:id="rId5"/>
     <hyperlink ref="I7" r:id="rId6"/>
+    <hyperlink ref="I8" r:id="rId7"/>
+    <hyperlink ref="I9" r:id="rId8"/>
+    <hyperlink ref="I10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
